--- a/survey_templates/036_household_survey--survey_templates.xlsx
+++ b/survey_templates/036_household_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,8 +442,8 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +640,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Household Income</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,20 +663,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Household Expenses</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,17 +686,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Household Address</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Enter your household's address</t>
-        </is>
-      </c>
+          <t>Household Survey Form 8</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -713,24 +709,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Household Phone</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Enter your household's phone number</t>
-        </is>
-      </c>
+          <t>Monthly Income</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -740,13 +732,13 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Household Members</t>
+          <t>Monthly Expenses</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -763,13 +755,13 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Household Address</t>
+          <t>Household Income Per Person</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -786,13 +778,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Household Expenses</t>
+          <t>Outdoor Features</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -807,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -840,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -857,29 +849,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>3-4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>household_survey_form_5_choices</t>
+          <t>household_survey_form_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>5_or_more</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>5 or more</t>
         </is>
       </c>
     </row>
@@ -891,46 +883,80 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>rent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Rent</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>household_survey_form_10_choices</t>
+          <t>household_survey_form_5_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>buy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Buy</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>household_survey_form_10_choices</t>
+          <t>household_survey_form_8_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>adults_only</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Adults Only</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>household_survey_form_8_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>children_only</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Children Only</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>household_survey_form_8_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>family</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Family</t>
         </is>
       </c>
     </row>
